--- a/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-patient-ins.xlsx
+++ b/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-patient-ins.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-07T12:22:36+00:00</t>
+    <t>2026-09-17T12:59:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-patient-ins.xlsx
+++ b/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-patient-ins.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-17T12:59:08+00:00</t>
+    <t>2026-09-28T13:01:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1327,7 +1327,7 @@
     <t>methodCollection</t>
   </si>
   <si>
-    <t>Canal d'obtention des traits d'identité ou du matricule INS (SM, CV, INSi, CB, RFID, AV) | Channel used to collect the identity traits or the INS identifier</t>
+    <t>Canal d'obtention des traits d'identité (SM, CV, INSi, CB, RFID, AV) | Channel used to collect the identity traits</t>
   </si>
   <si>
     <t>Précise le canal par lequel les traits d'identité ou le matricule INS ont été obtenus : saisie manuelle, lecture de la carte Vitale, interrogation directe du téléservice INSi, scan d'un code à barre/Datamatrix, lecture RFID ou Application carte Vitale. Ce champ ne porte pas le statut de confiance résultant (cf. sous-extension `identityStatus`) ni la pièce justificative contrôlée (cf. sous-extension `validationMode`).</t>

--- a/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-patient-ins.xlsx
+++ b/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-patient-ins.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-28T14:15:25+00:00</t>
+    <t>2026-09-28T14:29:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-patient-ins.xlsx
+++ b/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-patient-ins.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-28T14:29:01+00:00</t>
+    <t>2026-09-28T14:57:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-patient-ins.xlsx
+++ b/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-patient-ins.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-28T14:57:10+00:00</t>
+    <t>2026-09-29T08:00:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-patient-ins.xlsx
+++ b/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-patient-ins.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-29T08:00:45+00:00</t>
+    <t>2026-09-29T11:55:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-patient-ins.xlsx
+++ b/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-patient-ins.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-13T07:30:19+00:00</t>
+    <t>2026-10-13T07:53:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
